--- a/ig/DM-JUIN-2026/CodeSystem-tre-r410-perimetre-interruption-exercice.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-tre-r410-perimetre-interruption-exercice.xlsx
@@ -211,7 +211,7 @@
     <t>Totale</t>
   </si>
   <si>
-    <t>Interdiction d’exercer l’ensemble des activités de la profession concernée</t>
+    <t>Interruption d’exercice concernant l’ensemble des activités de la profession concernée</t>
   </si>
   <si>
     <t>P</t>
@@ -220,7 +220,7 @@
     <t>Partielle</t>
   </si>
   <si>
-    <t>Restriction limitée à certaines activités ou modalités d’exercice de la profession (par exemple, selon le type de patientèle), les autres activités ou modalités restant autorisées</t>
+    <t>Interruption d’exercice limitée à certaines activités ou modalités d’exercice de la profession concernée (par exemple, selon le type de patientèle) et n'impactant pas les autres activités ou modalités</t>
   </si>
 </sst>
 </file>
